--- a/Next Level Excel.xlsx
+++ b/Next Level Excel.xlsx
@@ -240,7 +240,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -600,6 +600,15 @@
       <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -855,7 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:E23"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.453125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="58" min="1" max="1"/>
@@ -863,6 +872,7 @@
     <col width="8.449999999999999" customWidth="1" style="58" min="6" max="16384"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="17.35" customHeight="1" s="59">
       <c r="A2" s="60" t="inlineStr">
         <is>
@@ -877,41 +887,47 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="59">
-      <c r="A5" s="62" t="inlineStr">
+      <c r="A5" s="114" t="inlineStr">
         <is>
           <t>Job Name:</t>
         </is>
       </c>
-      <c r="D5" s="62" t="inlineStr">
+      <c r="B5" s="115" t="n"/>
+      <c r="D5" s="114" t="inlineStr">
         <is>
           <t>Date:</t>
         </is>
       </c>
+      <c r="E5" s="115" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="62" t="inlineStr">
+      <c r="A6" s="114" t="inlineStr">
         <is>
           <t>Customer Name:</t>
         </is>
       </c>
-      <c r="D6" s="62" t="n"/>
+      <c r="B6" s="115" t="n"/>
+      <c r="D6" s="114" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="59">
-      <c r="A7" s="62" t="inlineStr">
+      <c r="A7" s="114" t="inlineStr">
         <is>
           <t>Customer Address:</t>
         </is>
       </c>
-      <c r="D7" s="62" t="n"/>
+      <c r="B7" s="115" t="n"/>
+      <c r="D7" s="114" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="59">
-      <c r="A8" s="62" t="inlineStr">
+      <c r="A8" s="114" t="inlineStr">
         <is>
           <t>Customer Phone:</t>
         </is>
       </c>
-      <c r="D8" s="62" t="n"/>
+      <c r="B8" s="115" t="n"/>
+      <c r="D8" s="114" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="59"/>
     <row r="10" ht="15" customHeight="1" s="59">
@@ -1174,10 +1190,10 @@
       <c r="E23" s="86" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="aa8c"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1187,7 +1203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:G46"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.453125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="58" min="1" max="1"/>
@@ -1196,6 +1212,7 @@
     <col width="8.449999999999999" customWidth="1" style="58" min="8" max="16384"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="15" customHeight="1" s="59">
       <c r="A2" s="89" t="inlineStr">
         <is>
@@ -1652,7 +1669,7 @@
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="59">
-      <c r="A30" s="100" t="inlineStr">
+      <c r="A30" s="96" t="inlineStr">
         <is>
           <t>Dump Fee</t>
         </is>
@@ -1691,6 +1708,8 @@
         <v/>
       </c>
     </row>
+    <row r="32"/>
+    <row r="33"/>
     <row r="34" ht="15" customHeight="1" s="59">
       <c r="A34" s="105" t="inlineStr">
         <is>
@@ -1944,10 +1963,10 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="aa8c"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1957,7 +1976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F51"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.453125" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="46" customWidth="1" style="58" min="1" max="1"/>
@@ -1965,6 +1984,7 @@
     <col width="8.449999999999999" customWidth="1" style="58" min="7" max="16384"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="15" customHeight="1" s="59">
       <c r="A2" s="89" t="inlineStr">
         <is>
@@ -2023,7 +2043,7 @@
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="59">
-      <c r="A5" s="91" t="inlineStr">
+      <c r="A5" s="116" t="inlineStr">
         <is>
           <t>#Demolition</t>
         </is>
@@ -2127,7 +2147,7 @@
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="59">
-      <c r="A10" s="96" t="inlineStr">
+      <c r="A10" s="100" t="inlineStr">
         <is>
           <t>#Carpentry</t>
         </is>
@@ -2451,7 +2471,7 @@
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="59">
-      <c r="A26" s="91" t="inlineStr">
+      <c r="A26" s="116" t="inlineStr">
         <is>
           <t>#Plumbing</t>
         </is>
@@ -2635,7 +2655,7 @@
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="59">
-      <c r="A35" s="91" t="inlineStr">
+      <c r="A35" s="116" t="inlineStr">
         <is>
           <t>#Electrical</t>
         </is>
@@ -2982,10 +3002,10 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="aa8c"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -2993,7 +3013,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
@@ -3043,7 +3063,7 @@
       </c>
     </row>
     <row r="2" ht="13.8" customHeight="1" s="59">
-      <c r="A2" s="106" t="inlineStr">
+      <c r="A2" s="58" t="inlineStr">
         <is>
           <t>#Plumbing</t>
         </is>
@@ -3127,7 +3147,7 @@
       </c>
     </row>
     <row r="6" ht="13.8" customHeight="1" s="59">
-      <c r="A6" s="106" t="inlineStr">
+      <c r="A6" s="58" t="inlineStr">
         <is>
           <t>#Electrical</t>
         </is>
@@ -3211,7 +3231,7 @@
       </c>
     </row>
     <row r="10" ht="13.8" customHeight="1" s="59">
-      <c r="A10" s="106" t="inlineStr">
+      <c r="A10" s="58" t="inlineStr">
         <is>
           <t>#Drywall</t>
         </is>
@@ -3295,7 +3315,7 @@
       </c>
     </row>
     <row r="14" ht="13.8" customHeight="1" s="59">
-      <c r="A14" s="106" t="inlineStr">
+      <c r="A14" s="58" t="inlineStr">
         <is>
           <t>#Masonry</t>
         </is>
@@ -3379,7 +3399,7 @@
       </c>
     </row>
     <row r="18" ht="13.8" customHeight="1" s="59">
-      <c r="A18" s="106" t="inlineStr">
+      <c r="A18" s="58" t="inlineStr">
         <is>
           <t>#Painting</t>
         </is>
@@ -3523,10 +3543,10 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="aa8c"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;KffffffPage &amp;P</oddFooter>
